--- a/data.xlsx
+++ b/data.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Emergency" sheetId="3" r:id="rId3"/>
     <sheet name="Services" sheetId="4" r:id="rId4"/>
     <sheet name="Residents" sheetId="5" r:id="rId5"/>
+    <sheet name="Documents" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -402,10 +403,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
-  <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -473,13 +470,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E6"/>
-  <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -593,12 +583,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D6"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="19.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -694,12 +678,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D11"/>
-  <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -865,14 +843,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F16"/>
-  <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1199,4 +1169,107 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F16"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="46.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="C1" t="str">
+        <v>File</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Updated</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Society Bye-Laws (2024 revision)</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Governance</v>
+      </c>
+      <c r="C2" t="str">
+        <v>materials/Society_Bye_Laws_2024.pdf</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2024-06-18</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Registered bye-laws currently in force</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AGM Minutes 2025</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Governance</v>
+      </c>
+      <c r="C3" t="str">
+        <v>materials/AGM_Minutes_2025.pdf</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2025-09-20</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Annual general meeting, 14 September 2025</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Maintenance &amp; Water Circular</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Circulars</v>
+      </c>
+      <c r="C4" t="str">
+        <v>materials/Maintenance_Circular_Aug_2025.pdf</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2025-08-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Payment dates and revised water timings</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Flat Transfer Application Form</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Forms</v>
+      </c>
+      <c r="C5" t="str">
+        <v>materials/Flat_Transfer_Form.pdf</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2024-11-02</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Submit to the society office with enclosures</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -7,8 +7,9 @@
     <sheet name="Committee" sheetId="2" r:id="rId2"/>
     <sheet name="Emergency" sheetId="3" r:id="rId3"/>
     <sheet name="Services" sheetId="4" r:id="rId4"/>
-    <sheet name="Residents" sheetId="5" r:id="rId5"/>
-    <sheet name="Documents" sheetId="6" r:id="rId6"/>
+    <sheet name="House Help" sheetId="5" r:id="rId5"/>
+    <sheet name="Residents" sheetId="6" r:id="rId6"/>
+    <sheet name="Documents" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -842,6 +843,245 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="32.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Role</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Charges</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Timings</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sunita Bai</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Maid</v>
+      </c>
+      <c r="C2" t="str">
+        <v>₹50 / visit</v>
+      </c>
+      <c r="D2" t="str">
+        <v>7 AM – 11 AM</v>
+      </c>
+      <c r="E2" t="str">
+        <v>+91 90210 33001</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Sweeping, mopping, utensils</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Lata Devi</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Maid</v>
+      </c>
+      <c r="C3" t="str">
+        <v>₹60 / visit</v>
+      </c>
+      <c r="D3" t="str">
+        <v>6 AM – 10 AM</v>
+      </c>
+      <c r="E3" t="str">
+        <v>+91 90210 33002</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Also does ironing on request</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Ramesh Yadav</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Plumber</v>
+      </c>
+      <c r="C4" t="str">
+        <v>₹100 / visit</v>
+      </c>
+      <c r="D4" t="str">
+        <v>On call, 8 AM – 8 PM</v>
+      </c>
+      <c r="E4" t="str">
+        <v>+91 90210 33003</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Parts charged separately</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Naresh Bhoir</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Electrician</v>
+      </c>
+      <c r="C5" t="str">
+        <v>₹120 / visit</v>
+      </c>
+      <c r="D5" t="str">
+        <v>On call, 9 AM – 8 PM</v>
+      </c>
+      <c r="E5" t="str">
+        <v>+91 90210 33004</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Wiring, fans, MCB</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Kamla Bai</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Cook</v>
+      </c>
+      <c r="C6" t="str">
+        <v>₹2,500 / month</v>
+      </c>
+      <c r="D6" t="str">
+        <v>11 AM – 2 PM</v>
+      </c>
+      <c r="E6" t="str">
+        <v>+91 90210 33005</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Vegetarian, 2 meals a day</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Imran Shaikh</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Car Cleaning</v>
+      </c>
+      <c r="C7" t="str">
+        <v>₹500 / month</v>
+      </c>
+      <c r="D7" t="str">
+        <v>6 AM – 9 AM</v>
+      </c>
+      <c r="E7" t="str">
+        <v>+91 90210 33006</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Daily wash, weekly interior</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Deepak Sawant</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Driver</v>
+      </c>
+      <c r="C8" t="str">
+        <v>₹300 / trip</v>
+      </c>
+      <c r="D8" t="str">
+        <v>By appointment</v>
+      </c>
+      <c r="E8" t="str">
+        <v>+91 90210 33007</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Local trips, own licence</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Anita Kamble</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Baby Sitter</v>
+      </c>
+      <c r="C9" t="str">
+        <v>₹150 / hour</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Flexible</v>
+      </c>
+      <c r="E9" t="str">
+        <v>+91 90210 33008</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Experienced with toddlers</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Salim Ansari</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Carpenter</v>
+      </c>
+      <c r="C10" t="str">
+        <v>₹150 / visit</v>
+      </c>
+      <c r="D10" t="str">
+        <v>On call</v>
+      </c>
+      <c r="E10" t="str">
+        <v>+91 90210 33009</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Furniture repair, fittings</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Ganesh Pawar</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Gardener</v>
+      </c>
+      <c r="C11" t="str">
+        <v>₹80 / visit</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Tue &amp; Sat mornings</v>
+      </c>
+      <c r="E11" t="str">
+        <v>+91 90210 33010</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Balcony plants, terrace garden</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F16"/>
   <sheetData>
     <row r="1">
@@ -1171,16 +1411,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <cols>
-    <col min="1" max="1" width="34.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="46.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/data.xlsx
+++ b/data.xlsx
@@ -6,10 +6,9 @@
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Committee" sheetId="2" r:id="rId2"/>
     <sheet name="Emergency" sheetId="3" r:id="rId3"/>
-    <sheet name="Services" sheetId="4" r:id="rId4"/>
-    <sheet name="House Help" sheetId="5" r:id="rId5"/>
-    <sheet name="Residents" sheetId="6" r:id="rId6"/>
-    <sheet name="Documents" sheetId="7" r:id="rId7"/>
+    <sheet name="Services &amp; Help" sheetId="4" r:id="rId4"/>
+    <sheet name="Residents" sheetId="5" r:id="rId5"/>
+    <sheet name="Documents" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -678,409 +677,404 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F19"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="37.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Service</v>
+        <v>Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Contact</v>
+        <v>Role</v>
       </c>
       <c r="C1" t="str">
+        <v>Charges</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Timings</v>
+      </c>
+      <c r="E1" t="str">
         <v>Phone</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>Notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Santosh Gupta</v>
+      </c>
+      <c r="B2" t="str">
         <v>Plumber</v>
       </c>
-      <c r="B2" t="str">
-        <v>Santosh Gupta</v>
-      </c>
       <c r="C2" t="str">
+        <v>₹100 / visit</v>
+      </c>
+      <c r="D2" t="str">
+        <v>8 AM – 8 PM, on call</v>
+      </c>
+      <c r="E2" t="str">
         <v>+91 90040 55511</v>
       </c>
-      <c r="D2" t="str">
-        <v>9 AM – 7 PM</v>
+      <c r="F2" t="str">
+        <v>Parts charged separately</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Naresh Bhoir</v>
+      </c>
+      <c r="B3" t="str">
         <v>Electrician</v>
       </c>
-      <c r="B3" t="str">
-        <v>Naresh Bhoir</v>
-      </c>
       <c r="C3" t="str">
+        <v>₹120 / visit</v>
+      </c>
+      <c r="D3" t="str">
+        <v>9 AM – 8 PM, on call</v>
+      </c>
+      <c r="E3" t="str">
         <v>+91 90040 55512</v>
       </c>
-      <c r="D3" t="str">
-        <v>9 AM – 8 PM</v>
+      <c r="F3" t="str">
+        <v>Wiring, fans, MCB</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Lift Technician</v>
+        <v>Salim Ansari</v>
       </c>
       <c r="B4" t="str">
-        <v>Otis Service</v>
+        <v>Carpenter</v>
       </c>
       <c r="C4" t="str">
-        <v>+91 90040 55513</v>
+        <v>₹150 / visit</v>
       </c>
       <c r="D4" t="str">
-        <v>AMC — 4 hr response</v>
+        <v>On call</v>
+      </c>
+      <c r="E4" t="str">
+        <v>+91 90210 33009</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Furniture repair and fittings</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Pest Control</v>
+        <v>Otis Service</v>
       </c>
       <c r="B5" t="str">
-        <v>HiCare</v>
+        <v>Lift Technician</v>
       </c>
       <c r="C5" t="str">
-        <v>+91 90040 55514</v>
+        <v>Society AMC</v>
       </c>
       <c r="D5" t="str">
-        <v>Quarterly, by booking</v>
+        <v>4-hour response</v>
+      </c>
+      <c r="E5" t="str">
+        <v>+91 90040 55513</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Report faults to the manager first</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Housekeeping</v>
+        <v>HiCare</v>
       </c>
       <c r="B6" t="str">
-        <v>Shanti Devi</v>
+        <v>Pest Control</v>
       </c>
       <c r="C6" t="str">
-        <v>+91 90040 55515</v>
+        <v>₹1,200 / flat</v>
       </c>
       <c r="D6" t="str">
-        <v>6 AM – 2 PM</v>
+        <v>By appointment</v>
+      </c>
+      <c r="E6" t="str">
+        <v>+91 90040 55514</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Quarterly society drive is free</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Water Tanker</v>
+        <v>Shanti Devi</v>
       </c>
       <c r="B7" t="str">
-        <v>Jai Bhavani</v>
+        <v>Housekeeping</v>
       </c>
       <c r="C7" t="str">
-        <v>+91 90040 55521</v>
+        <v>Society staff</v>
       </c>
       <c r="D7" t="str">
-        <v>Same-day delivery</v>
+        <v>6 AM – 2 PM</v>
+      </c>
+      <c r="E7" t="str">
+        <v>+91 90040 55515</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Common areas and staircases</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Electricity Board</v>
+        <v>Ganesh Pawar</v>
       </c>
       <c r="B8" t="str">
-        <v>MSEDCL</v>
+        <v>Gardener</v>
       </c>
       <c r="C8" t="str">
-        <v>1912</v>
+        <v>₹80 / visit</v>
       </c>
       <c r="D8" t="str">
-        <v>Outage helpline</v>
+        <v>Tue &amp; Sat mornings</v>
+      </c>
+      <c r="E8" t="str">
+        <v>+91 90210 33010</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Balcony and terrace plants</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Gas Agency</v>
+        <v>Jai Bhavani</v>
       </c>
       <c r="B9" t="str">
-        <v>Mahanagar Gas</v>
+        <v>Water Tanker</v>
       </c>
       <c r="C9" t="str">
-        <v>+91 90040 55522</v>
+        <v>₹900 / tanker</v>
       </c>
       <c r="D9" t="str">
-        <v>Leak: 1800 22 9944</v>
+        <v>Same-day delivery</v>
+      </c>
+      <c r="E9" t="str">
+        <v>+91 90040 55521</v>
+      </c>
+      <c r="F9" t="str">
+        <v>10,000 litre tanker</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Society Manager</v>
+        <v>MSEDCL</v>
       </c>
       <c r="B10" t="str">
-        <v>D. Kamble</v>
+        <v>Electricity Board</v>
       </c>
       <c r="C10" t="str">
-        <v>+91 90040 55531</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>Mon–Sat, 10 AM – 6 PM</v>
+        <v>24x7 helpline</v>
+      </c>
+      <c r="E10" t="str">
+        <v>1912</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Outages and meter faults</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>Mahanagar Gas</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Gas Agency</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>24x7 for leaks</v>
+      </c>
+      <c r="E11" t="str">
+        <v>+91 90040 55522</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Leak helpline 1800 22 9944</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>D. Kamble</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Society Manager</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>Mon–Sat, 10 AM – 6 PM</v>
+      </c>
+      <c r="E12" t="str">
+        <v>+91 90040 55531</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Maintenance bills, NOCs, complaints</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>S. Rane</v>
+      </c>
+      <c r="B13" t="str">
         <v>Accountant</v>
       </c>
-      <c r="B11" t="str">
-        <v>S. Rane</v>
-      </c>
-      <c r="C11" t="str">
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>Tue &amp; Thu, 4 PM – 7 PM</v>
+      </c>
+      <c r="E13" t="str">
         <v>+91 90040 55532</v>
       </c>
-      <c r="D11" t="str">
-        <v>Tue &amp; Thu, 4 PM – 7 PM</v>
+      <c r="F13" t="str">
+        <v>Dues, receipts, statements</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Sunita Bai</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Maid</v>
+      </c>
+      <c r="C14" t="str">
+        <v>₹50 / visit</v>
+      </c>
+      <c r="D14" t="str">
+        <v>7 AM – 11 AM</v>
+      </c>
+      <c r="E14" t="str">
+        <v>+91 90210 33001</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Sweeping, mopping, utensils</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Lata Devi</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Maid</v>
+      </c>
+      <c r="C15" t="str">
+        <v>₹60 / visit</v>
+      </c>
+      <c r="D15" t="str">
+        <v>6 AM – 10 AM</v>
+      </c>
+      <c r="E15" t="str">
+        <v>+91 90210 33002</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Also irons clothes on request</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Kamla Bai</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Cook</v>
+      </c>
+      <c r="C16" t="str">
+        <v>₹2,500 / month</v>
+      </c>
+      <c r="D16" t="str">
+        <v>11 AM – 2 PM</v>
+      </c>
+      <c r="E16" t="str">
+        <v>+91 90210 33005</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Vegetarian, two meals a day</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Imran Shaikh</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Car Cleaning</v>
+      </c>
+      <c r="C17" t="str">
+        <v>₹500 / month</v>
+      </c>
+      <c r="D17" t="str">
+        <v>6 AM – 9 AM</v>
+      </c>
+      <c r="E17" t="str">
+        <v>+91 90210 33006</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Daily wash, interior weekly</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Deepak Sawant</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Driver</v>
+      </c>
+      <c r="C18" t="str">
+        <v>₹300 / trip</v>
+      </c>
+      <c r="D18" t="str">
+        <v>By appointment</v>
+      </c>
+      <c r="E18" t="str">
+        <v>+91 90210 33007</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Local trips, holds a valid licence</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Anita Kamble</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Baby Sitter</v>
+      </c>
+      <c r="C19" t="str">
+        <v>₹150 / hour</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Flexible</v>
+      </c>
+      <c r="E19" t="str">
+        <v>+91 90210 33008</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Experienced with toddlers</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Role</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Charges</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Timings</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Sunita Bai</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Maid</v>
-      </c>
-      <c r="C2" t="str">
-        <v>₹50 / visit</v>
-      </c>
-      <c r="D2" t="str">
-        <v>7 AM – 11 AM</v>
-      </c>
-      <c r="E2" t="str">
-        <v>+91 90210 33001</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Sweeping, mopping, utensils</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Lata Devi</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Maid</v>
-      </c>
-      <c r="C3" t="str">
-        <v>₹60 / visit</v>
-      </c>
-      <c r="D3" t="str">
-        <v>6 AM – 10 AM</v>
-      </c>
-      <c r="E3" t="str">
-        <v>+91 90210 33002</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Also does ironing on request</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Ramesh Yadav</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Plumber</v>
-      </c>
-      <c r="C4" t="str">
-        <v>₹100 / visit</v>
-      </c>
-      <c r="D4" t="str">
-        <v>On call, 8 AM – 8 PM</v>
-      </c>
-      <c r="E4" t="str">
-        <v>+91 90210 33003</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Parts charged separately</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Naresh Bhoir</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Electrician</v>
-      </c>
-      <c r="C5" t="str">
-        <v>₹120 / visit</v>
-      </c>
-      <c r="D5" t="str">
-        <v>On call, 9 AM – 8 PM</v>
-      </c>
-      <c r="E5" t="str">
-        <v>+91 90210 33004</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Wiring, fans, MCB</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Kamla Bai</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Cook</v>
-      </c>
-      <c r="C6" t="str">
-        <v>₹2,500 / month</v>
-      </c>
-      <c r="D6" t="str">
-        <v>11 AM – 2 PM</v>
-      </c>
-      <c r="E6" t="str">
-        <v>+91 90210 33005</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Vegetarian, 2 meals a day</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Imran Shaikh</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Car Cleaning</v>
-      </c>
-      <c r="C7" t="str">
-        <v>₹500 / month</v>
-      </c>
-      <c r="D7" t="str">
-        <v>6 AM – 9 AM</v>
-      </c>
-      <c r="E7" t="str">
-        <v>+91 90210 33006</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Daily wash, weekly interior</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Deepak Sawant</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Driver</v>
-      </c>
-      <c r="C8" t="str">
-        <v>₹300 / trip</v>
-      </c>
-      <c r="D8" t="str">
-        <v>By appointment</v>
-      </c>
-      <c r="E8" t="str">
-        <v>+91 90210 33007</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Local trips, own licence</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Anita Kamble</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Baby Sitter</v>
-      </c>
-      <c r="C9" t="str">
-        <v>₹150 / hour</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Flexible</v>
-      </c>
-      <c r="E9" t="str">
-        <v>+91 90210 33008</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Experienced with toddlers</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Salim Ansari</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Carpenter</v>
-      </c>
-      <c r="C10" t="str">
-        <v>₹150 / visit</v>
-      </c>
-      <c r="D10" t="str">
-        <v>On call</v>
-      </c>
-      <c r="E10" t="str">
-        <v>+91 90210 33009</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Furniture repair, fittings</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Ganesh Pawar</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Gardener</v>
-      </c>
-      <c r="C11" t="str">
-        <v>₹80 / visit</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Tue &amp; Sat mornings</v>
-      </c>
-      <c r="E11" t="str">
-        <v>+91 90210 33010</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Balcony plants, terrace garden</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F16"/>
   <sheetData>
@@ -1411,7 +1405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -402,7 +402,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,9 +464,25 @@
         <v>NBOM/HSG/1284/2009</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Confidential Notice</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Please do not forward this link or share these details with anyone outside the society.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Note: Services &amp; Help</v>
+      </c>
+      <c r="B9" t="str">
+        <v>These contacts are collected from fellow residents. The society has not verified, screened or endorsed any of them. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -678,14 +698,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F19"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="37.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/data.xlsx
+++ b/data.xlsx
@@ -403,10 +403,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
-  <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1088,7 +1084,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:I16"/>
+  <cols>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1109,6 +1116,15 @@
       <c r="F1" t="str">
         <v>Type</v>
       </c>
+      <c r="G1" t="str">
+        <v>Owner Name</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Owner Phone</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Owner Address</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1129,6 +1145,15 @@
       <c r="F2" t="str">
         <v>Owner</v>
       </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1149,6 +1174,15 @@
       <c r="F3" t="str">
         <v>Owner</v>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1169,6 +1203,15 @@
       <c r="F4" t="str">
         <v>Tenant</v>
       </c>
+      <c r="G4" t="str">
+        <v>Sanjay Kulkarni</v>
+      </c>
+      <c r="H4" t="str">
+        <v>+91 98200 44001</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Flat 9, Sunrise Apartments, Aundh, Pune 411007</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1189,6 +1232,15 @@
       <c r="F5" t="str">
         <v>Owner</v>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1209,6 +1261,15 @@
       <c r="F6" t="str">
         <v>Owner</v>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1229,6 +1290,15 @@
       <c r="F7" t="str">
         <v>Owner</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1249,6 +1319,15 @@
       <c r="F8" t="str">
         <v>Owner</v>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1269,6 +1348,15 @@
       <c r="F9" t="str">
         <v>Tenant</v>
       </c>
+      <c r="G9" t="str">
+        <v>Rajesh Menon</v>
+      </c>
+      <c r="H9" t="str">
+        <v>+91 98200 44002</v>
+      </c>
+      <c r="I9" t="str">
+        <v>B-201, Green Valley Residency (resident owner)</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1289,6 +1377,15 @@
       <c r="F10" t="str">
         <v>Owner</v>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1309,6 +1406,15 @@
       <c r="F11" t="str">
         <v>Owner</v>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1329,6 +1435,15 @@
       <c r="F12" t="str">
         <v>Owner</v>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1349,6 +1464,15 @@
       <c r="F13" t="str">
         <v>Tenant</v>
       </c>
+      <c r="G13" t="str">
+        <v>Farida Merchant</v>
+      </c>
+      <c r="H13" t="str">
+        <v>+91 98200 44003</v>
+      </c>
+      <c r="I13" t="str">
+        <v>22 Peddar Road, Mumbai 400026</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1369,6 +1493,15 @@
       <c r="F14" t="str">
         <v>Owner</v>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1389,6 +1522,15 @@
       <c r="F15" t="str">
         <v>Owner</v>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1409,10 +1551,19 @@
       <c r="F16" t="str">
         <v>Owner</v>
       </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -402,7 +402,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B16"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="90.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -476,9 +480,65 @@
         <v>These contacts are collected from fellow residents. The society has not verified, screened or endorsed any of them. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Hindi: Committee</v>
+      </c>
+      <c r="B10" t="str">
+        <v>समिति</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Hindi: Emergency</v>
+      </c>
+      <c r="B11" t="str">
+        <v>आपातकालीन संपर्क</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Hindi: Services &amp; Help</v>
+      </c>
+      <c r="B12" t="str">
+        <v>सेवाएँ और सहायता</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Hindi: Residents</v>
+      </c>
+      <c r="B13" t="str">
+        <v>निवासी</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Hindi: Documents</v>
+      </c>
+      <c r="B14" t="str">
+        <v>दस्तावेज़</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Confidential HI</v>
+      </c>
+      <c r="B15" t="str">
+        <v>कृपया यह लिंक या विवरण सोसाइटी के बाहर किसी के साथ साझा न करें।</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Note HI: Services &amp; Help</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ये संपर्क अन्य निवासियों द्वारा दिए गए हैं। सोसाइटी ने इनकी जाँच नहीं की है। काम शुरू कराने से पहले कृपया स्वयं पुष्टि करें और शुल्क तय कर लें — जोखिम आपका अपना होगा।</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1085,17 +1145,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I16"/>
-  <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="48.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Services &amp; Help" sheetId="4" r:id="rId4"/>
     <sheet name="Residents" sheetId="5" r:id="rId5"/>
     <sheet name="Documents" sheetId="6" r:id="rId6"/>
+    <sheet name="Services" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -402,10 +403,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B7"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="90.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -421,7 +422,7 @@
         <v>Society Name</v>
       </c>
       <c r="B2" t="str">
-        <v>Green Valley Residency</v>
+        <v>Laxmi venkatesh Nagar</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +430,7 @@
         <v>Tagline</v>
       </c>
       <c r="B3" t="str">
-        <v>A Co-operative Housing Society</v>
+        <v>Best Housing Society in Ichalkaranji</v>
       </c>
     </row>
     <row r="4">
@@ -437,7 +438,7 @@
         <v>Address</v>
       </c>
       <c r="B4" t="str">
-        <v>Plot 14, Sector 22, Kharghar</v>
+        <v>Old chandur road</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +446,7 @@
         <v>City</v>
       </c>
       <c r="B5" t="str">
-        <v>Navi Mumbai</v>
+        <v>ichalkaranji</v>
       </c>
     </row>
     <row r="6">
@@ -453,7 +454,7 @@
         <v>Pincode</v>
       </c>
       <c r="B6" t="str">
-        <v>410210</v>
+        <v>416115</v>
       </c>
     </row>
     <row r="7">
@@ -464,81 +465,9 @@
         <v>NBOM/HSG/1284/2009</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Confidential Notice</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Please do not forward this link or share these details with anyone outside the society.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Note: Services &amp; Help</v>
-      </c>
-      <c r="B9" t="str">
-        <v>These contacts are collected from fellow residents. The society has not verified, screened or endorsed any of them. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Hindi: Committee</v>
-      </c>
-      <c r="B10" t="str">
-        <v>समिति</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Hindi: Emergency</v>
-      </c>
-      <c r="B11" t="str">
-        <v>आपातकालीन संपर्क</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Hindi: Services &amp; Help</v>
-      </c>
-      <c r="B12" t="str">
-        <v>सेवाएँ और सहायता</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Hindi: Residents</v>
-      </c>
-      <c r="B13" t="str">
-        <v>निवासी</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Hindi: Documents</v>
-      </c>
-      <c r="B14" t="str">
-        <v>दस्तावेज़</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Confidential HI</v>
-      </c>
-      <c r="B15" t="str">
-        <v>कृपया यह लिंक या विवरण सोसाइटी के बाहर किसी के साथ साझा न करें।</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Note HI: Services &amp; Help</v>
-      </c>
-      <c r="B16" t="str">
-        <v>ये संपर्क अन्य निवासियों द्वारा दिए गए हैं। सोसाइटी ने इनकी जाँच नहीं की है। काम शुरू कराने से पहले कृपया स्वयं पुष्टि करें और शुल्क तय कर लें — जोखिम आपका अपना होगा।</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -546,6 +475,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E6"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -566,7 +502,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ramesh Iyer</v>
+        <v/>
       </c>
       <c r="B2" t="str">
         <v>Chairman</v>
@@ -575,15 +511,15 @@
         <v>A-402</v>
       </c>
       <c r="D2" t="str">
-        <v>+91 98200 11223</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>ramesh.iyer@example.com</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sunita Deshmukh</v>
+        <v/>
       </c>
       <c r="B3" t="str">
         <v>Hon. Secretary</v>
@@ -592,15 +528,15 @@
         <v>B-105</v>
       </c>
       <c r="D3" t="str">
-        <v>+91 98200 11224</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>sunita.d@example.com</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Farhan Qureshi</v>
+        <v/>
       </c>
       <c r="B4" t="str">
         <v>Treasurer</v>
@@ -609,15 +545,15 @@
         <v>A-701</v>
       </c>
       <c r="D4" t="str">
-        <v>+91 98200 11225</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>farhan.q@example.com</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Meera Nair</v>
+        <v/>
       </c>
       <c r="B5" t="str">
         <v>Committee Member</v>
@@ -626,15 +562,15 @@
         <v>C-203</v>
       </c>
       <c r="D5" t="str">
-        <v>+91 98200 11226</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>meera.nair@example.com</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Harpreet Singh</v>
+        <v/>
       </c>
       <c r="B6" t="str">
         <v>Committee Member</v>
@@ -643,7 +579,7 @@
         <v>B-604</v>
       </c>
       <c r="D6" t="str">
-        <v>+91 98200 11227</v>
+        <v/>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -659,6 +595,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D6"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -699,7 +641,7 @@
         <v>100</v>
       </c>
       <c r="D3" t="str">
-        <v>Kharghar station</v>
+        <v>Ich station</v>
       </c>
     </row>
     <row r="4">
@@ -721,7 +663,7 @@
         <v>Security Gate</v>
       </c>
       <c r="B5" t="str">
-        <v>Ravi Yadav</v>
+        <v/>
       </c>
       <c r="C5" t="str">
         <v>+91 90040 55501</v>
@@ -754,6 +696,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F19"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1144,7 +1094,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:F25"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1165,15 +1123,6 @@
       <c r="F1" t="str">
         <v>Type</v>
       </c>
-      <c r="G1" t="str">
-        <v>Owner Name</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Owner Phone</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Owner Address</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1186,21 +1135,12 @@
         <v>A-101</v>
       </c>
       <c r="D2" t="str">
-        <v>+91 98330 40011</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>anil.k@example.com</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
         <v/>
       </c>
     </row>
@@ -1215,21 +1155,12 @@
         <v>A-202</v>
       </c>
       <c r="D3" t="str">
-        <v>+91 98330 40012</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>priya.r@example.com</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
         <v/>
       </c>
     </row>
@@ -1244,22 +1175,13 @@
         <v>A-305</v>
       </c>
       <c r="D4" t="str">
-        <v>+91 98330 40013</v>
+        <v/>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Tenant</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Sanjay Kulkarni</v>
-      </c>
-      <c r="H4" t="str">
-        <v>+91 98200 44001</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Flat 9, Sunrise Apartments, Aundh, Pune 411007</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1273,21 +1195,12 @@
         <v>A-506</v>
       </c>
       <c r="D5" t="str">
-        <v>+91 98330 40014</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>kavita.j@example.com</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
         <v/>
       </c>
     </row>
@@ -1302,21 +1215,12 @@
         <v>A-608</v>
       </c>
       <c r="D6" t="str">
-        <v>+91 98330 40023</v>
+        <v/>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
         <v/>
       </c>
     </row>
@@ -1331,21 +1235,12 @@
         <v>B-201</v>
       </c>
       <c r="D7" t="str">
-        <v>+91 98330 40015</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
         <v/>
       </c>
     </row>
@@ -1360,21 +1255,12 @@
         <v>B-302</v>
       </c>
       <c r="D8" t="str">
-        <v>+91 98330 40016</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>deepa.c@example.com</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
         <v/>
       </c>
     </row>
@@ -1389,22 +1275,13 @@
         <v>B-403</v>
       </c>
       <c r="D9" t="str">
-        <v>+91 98330 40017</v>
+        <v/>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Tenant</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Rajesh Menon</v>
-      </c>
-      <c r="H9" t="str">
-        <v>+91 98200 44002</v>
-      </c>
-      <c r="I9" t="str">
-        <v>B-201, Green Valley Residency (resident owner)</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1418,21 +1295,12 @@
         <v>B-505</v>
       </c>
       <c r="D10" t="str">
-        <v>+91 98330 40018</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>nisha.p@example.com</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
         <v/>
       </c>
     </row>
@@ -1447,21 +1315,12 @@
         <v>B-707</v>
       </c>
       <c r="D11" t="str">
-        <v>+91 98330 40024</v>
+        <v/>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
         <v/>
       </c>
     </row>
@@ -1476,21 +1335,12 @@
         <v>C-102</v>
       </c>
       <c r="D12" t="str">
-        <v>+91 98330 40019</v>
+        <v/>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
         <v/>
       </c>
     </row>
@@ -1505,22 +1355,13 @@
         <v>C-304</v>
       </c>
       <c r="D13" t="str">
-        <v>+91 98330 40020</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>ayesha.k@example.com</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>Tenant</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Farida Merchant</v>
-      </c>
-      <c r="H13" t="str">
-        <v>+91 98200 44003</v>
-      </c>
-      <c r="I13" t="str">
-        <v>22 Peddar Road, Mumbai 400026</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1534,21 +1375,12 @@
         <v>C-405</v>
       </c>
       <c r="D14" t="str">
-        <v>+91 98330 40021</v>
+        <v/>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
         <v/>
       </c>
     </row>
@@ -1563,21 +1395,12 @@
         <v>C-506</v>
       </c>
       <c r="D15" t="str">
-        <v>+91 98330 40022</v>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <v>lakshmi.s@example.com</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
         <v/>
       </c>
     </row>
@@ -1592,27 +1415,198 @@
         <v>C-608</v>
       </c>
       <c r="D16" t="str">
-        <v>+91 98330 40025</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>tanvi.m@example.com</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Narendrakumar heda</v>
+      </c>
+      <c r="B17" t="str">
+        <v>B</v>
+      </c>
+      <c r="C17" t="str">
+        <v>11</v>
+      </c>
+      <c r="D17" t="str">
+        <v>8793109590</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Bhavesh Rajeshkumar Sarda</v>
+      </c>
+      <c r="B18" t="str">
+        <v>B</v>
+      </c>
+      <c r="C18" t="str">
+        <v>B-2</v>
+      </c>
+      <c r="D18" t="str">
+        <v>8482996010</v>
+      </c>
+      <c r="E18" t="str">
+        <v>bhaveshsarda2004@gmail.com</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Sagar Agarwal</v>
+      </c>
+      <c r="B19" t="str">
+        <v>A</v>
+      </c>
+      <c r="C19" t="str">
+        <v>A - 2</v>
+      </c>
+      <c r="D19" t="str">
+        <v>7350665037</v>
+      </c>
+      <c r="E19" t="str">
+        <v>agarwalsagar016@gmail.com</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Rahul Pareek</v>
+      </c>
+      <c r="B20" t="str">
+        <v>B</v>
+      </c>
+      <c r="C20" t="str">
+        <v>9</v>
+      </c>
+      <c r="D20" t="str">
+        <v>9156704040</v>
+      </c>
+      <c r="E20" t="str">
+        <v>rahulpareek3366@gmail.com</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Shrihari Narayan Makote</v>
+      </c>
+      <c r="B21" t="str">
+        <v>D</v>
+      </c>
+      <c r="C21" t="str">
+        <v>12</v>
+      </c>
+      <c r="D21" t="str">
+        <v>9922497427</v>
+      </c>
+      <c r="E21" t="str">
+        <v>shriharimakote70@gmail.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Ramdev Rathi</v>
+      </c>
+      <c r="B22" t="str">
+        <v>C</v>
+      </c>
+      <c r="C22" t="str">
+        <v>C2-C3</v>
+      </c>
+      <c r="D22" t="str">
+        <v>9422423985</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Pradeep Jhunjhunwala</v>
+      </c>
+      <c r="B23" t="str">
+        <v>A</v>
+      </c>
+      <c r="C23" t="str">
+        <v>A-10</v>
+      </c>
+      <c r="D23" t="str">
+        <v>9922114900</v>
+      </c>
+      <c r="E23" t="str">
+        <v>cool16yash@gmail.com</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Harishkumar Bharatkumar</v>
+      </c>
+      <c r="B24" t="str">
+        <v>C</v>
+      </c>
+      <c r="C24" t="str">
+        <v>C-14</v>
+      </c>
+      <c r="D24" t="str">
+        <v>7019426263</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Laxmi kant balkrishan malpani</v>
+      </c>
+      <c r="B25" t="str">
+        <v>A</v>
+      </c>
+      <c r="C25" t="str">
+        <v>A/1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>9372281026</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1620,6 +1614,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1711,4 +1712,175 @@
     <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D11"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Service</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Contact</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Plumber</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Electrician</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Lift Technician</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Pest Control</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Housekeeping</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Water Tanker</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Electricity Board</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Gas Agency</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Society Manager</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -465,9 +465,17 @@
         <v>NBOM/HSG/1284/2009</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Theme</v>
+      </c>
+      <c r="B8" t="str">
+        <v>slate</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -470,7 +470,7 @@
         <v>Theme</v>
       </c>
       <c r="B8" t="str">
-        <v>slate</v>
+        <v>paper</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10,6 +10,8 @@
     <sheet name="Residents" sheetId="5" r:id="rId5"/>
     <sheet name="Documents" sheetId="6" r:id="rId6"/>
     <sheet name="Services" sheetId="7" r:id="rId7"/>
+    <sheet name="_Private" sheetId="8" r:id="rId8"/>
+    <sheet name="_Read me" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -403,10 +405,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -416,13 +419,19 @@
       <c r="B1" t="str">
         <v>Value</v>
       </c>
+      <c r="C1" t="str">
+        <v>What it does / यह क्या करता है</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>Society Name</v>
       </c>
       <c r="B2" t="str">
-        <v>Laxmi venkatesh Nagar</v>
+        <v>LAXMI VENKATESH NAGAR</v>
+      </c>
+      <c r="C2" t="str">
+        <v>सोसाइटी का नाम — बड़े शीर्षक में दिखेगा</v>
       </c>
     </row>
     <row r="3">
@@ -430,7 +439,10 @@
         <v>Tagline</v>
       </c>
       <c r="B3" t="str">
-        <v>Best Housing Society in Ichalkaranji</v>
+        <v>The Best Society in ICHALKARANJI</v>
+      </c>
+      <c r="C3" t="str">
+        <v>उपशीर्षक</v>
       </c>
     </row>
     <row r="4">
@@ -440,13 +452,19 @@
       <c r="B4" t="str">
         <v>Old chandur road</v>
       </c>
+      <c r="C4" t="str">
+        <v>पता</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>City</v>
       </c>
       <c r="B5" t="str">
-        <v>ichalkaranji</v>
+        <v>Ichalkaranji</v>
+      </c>
+      <c r="C5" t="str">
+        <v>शहर</v>
       </c>
     </row>
     <row r="6">
@@ -456,33 +474,141 @@
       <c r="B6" t="str">
         <v>416115</v>
       </c>
+      <c r="C6" t="str">
+        <v>पिन कोड</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>Registration No</v>
       </c>
       <c r="B7" t="str">
-        <v>NBOM/HSG/1284/2009</v>
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>पंजीकरण संख्या — नीचे फुटर में</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>Logo</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>वैकल्पिक: लोगो की इमेज URL</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Confidential Notice</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Please do not forward this link or share these details with anyone outside the society.</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ऊपर दिखने वाली चेतावनी (अंग्रेज़ी)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Confidential HI</v>
+      </c>
+      <c r="B10" t="str">
+        <v>कृपया यह लिंक या विवरण सोसाइटी के बाहर किसी के साथ साझा न करें।</v>
+      </c>
+      <c r="C10" t="str">
+        <v>वही चेतावनी हिंदी में</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Theme</v>
       </c>
-      <c r="B8" t="str">
-        <v>paper</v>
+      <c r="B11" t="str">
+        <v>Paper</v>
+      </c>
+      <c r="C11" t="str">
+        <v>navy, forest, plum, slate, sunset, ocean, paper</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Hindi: Committee</v>
+      </c>
+      <c r="B12" t="str">
+        <v>समिति</v>
+      </c>
+      <c r="C12" t="str">
+        <v>हिंदी में अनुभाग का नाम</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Hindi: Emergency</v>
+      </c>
+      <c r="B13" t="str">
+        <v>आपातकालीन संपर्क</v>
+      </c>
+      <c r="C13" t="str">
+        <v>हिंदी में अनुभाग का नाम</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Hindi: Services &amp; Help</v>
+      </c>
+      <c r="B14" t="str">
+        <v>सेवाएँ और सहायता</v>
+      </c>
+      <c r="C14" t="str">
+        <v>हिंदी में अनुभाग का नाम</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Hindi: Residents</v>
+      </c>
+      <c r="B15" t="str">
+        <v>निवासी</v>
+      </c>
+      <c r="C15" t="str">
+        <v>हिंदी में अनुभाग का नाम</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Hindi: Documents</v>
+      </c>
+      <c r="B16" t="str">
+        <v>दस्तावेज़</v>
+      </c>
+      <c r="C16" t="str">
+        <v>हिंदी में अनुभाग का नाम</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Note: Services &amp; Help</v>
+      </c>
+      <c r="B17" t="str">
+        <v>These contacts are collected from members. They have not been verified or endorsed. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>उस अनुभाग के नीचे दिखने वाली चेतावनी</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -516,7 +642,7 @@
         <v>Chairman</v>
       </c>
       <c r="C2" t="str">
-        <v>A-402</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -533,76 +659,25 @@
         <v>Hon. Secretary</v>
       </c>
       <c r="C3" t="str">
-        <v>B-105</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v/>
       </c>
       <c r="E3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v>Treasurer</v>
-      </c>
-      <c r="C4" t="str">
-        <v>A-701</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v>Committee Member</v>
-      </c>
-      <c r="C5" t="str">
-        <v>C-203</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v>Committee Member</v>
-      </c>
-      <c r="C6" t="str">
-        <v>B-604</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -649,7 +724,7 @@
         <v>100</v>
       </c>
       <c r="D3" t="str">
-        <v>Ich station</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -663,7 +738,7 @@
         <v>101</v>
       </c>
       <c r="D4" t="str">
-        <v>Toll free, 24x7</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -671,32 +746,18 @@
         <v>Security Gate</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Example Name</v>
       </c>
       <c r="C5" t="str">
-        <v>+91 90040 55501</v>
+        <v>9.1E+12</v>
       </c>
       <c r="D5" t="str">
         <v>Main gate, 24x7</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Ndrf Helpline</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>108</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Disaster response</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -747,7 +808,7 @@
         <v>8 AM – 8 PM, on call</v>
       </c>
       <c r="E2" t="str">
-        <v>+91 90040 55511</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>Parts charged separately</v>
@@ -767,7 +828,7 @@
         <v>9 AM – 8 PM, on call</v>
       </c>
       <c r="E3" t="str">
-        <v>+91 90040 55512</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>Wiring, fans, MCB</v>
@@ -775,7 +836,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Salim Ansari</v>
+        <v>Jangid</v>
       </c>
       <c r="B4" t="str">
         <v>Carpenter</v>
@@ -787,7 +848,7 @@
         <v>On call</v>
       </c>
       <c r="E4" t="str">
-        <v>+91 90210 33009</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v>Furniture repair and fittings</v>
@@ -807,7 +868,7 @@
         <v>4-hour response</v>
       </c>
       <c r="E5" t="str">
-        <v>+91 90040 55513</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v>Report faults to the manager first</v>
@@ -827,7 +888,7 @@
         <v>By appointment</v>
       </c>
       <c r="E6" t="str">
-        <v>+91 90040 55514</v>
+        <v/>
       </c>
       <c r="F6" t="str">
         <v>Quarterly society drive is free</v>
@@ -847,7 +908,7 @@
         <v>6 AM – 2 PM</v>
       </c>
       <c r="E7" t="str">
-        <v>+91 90040 55515</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v>Common areas and staircases</v>
@@ -867,7 +928,7 @@
         <v>Tue &amp; Sat mornings</v>
       </c>
       <c r="E8" t="str">
-        <v>+91 90210 33010</v>
+        <v/>
       </c>
       <c r="F8" t="str">
         <v>Balcony and terrace plants</v>
@@ -887,7 +948,7 @@
         <v>Same-day delivery</v>
       </c>
       <c r="E9" t="str">
-        <v>+91 90040 55521</v>
+        <v/>
       </c>
       <c r="F9" t="str">
         <v>10,000 litre tanker</v>
@@ -907,7 +968,7 @@
         <v>24x7 helpline</v>
       </c>
       <c r="E10" t="str">
-        <v>1912</v>
+        <v/>
       </c>
       <c r="F10" t="str">
         <v>Outages and meter faults</v>
@@ -927,7 +988,7 @@
         <v>24x7 for leaks</v>
       </c>
       <c r="E11" t="str">
-        <v>+91 90040 55522</v>
+        <v/>
       </c>
       <c r="F11" t="str">
         <v>Leak helpline 1800 22 9944</v>
@@ -947,7 +1008,7 @@
         <v>Mon–Sat, 10 AM – 6 PM</v>
       </c>
       <c r="E12" t="str">
-        <v>+91 90040 55531</v>
+        <v/>
       </c>
       <c r="F12" t="str">
         <v>Maintenance bills, NOCs, complaints</v>
@@ -967,7 +1028,7 @@
         <v>Tue &amp; Thu, 4 PM – 7 PM</v>
       </c>
       <c r="E13" t="str">
-        <v>+91 90040 55532</v>
+        <v/>
       </c>
       <c r="F13" t="str">
         <v>Dues, receipts, statements</v>
@@ -987,7 +1048,7 @@
         <v>7 AM – 11 AM</v>
       </c>
       <c r="E14" t="str">
-        <v>+91 90210 33001</v>
+        <v/>
       </c>
       <c r="F14" t="str">
         <v>Sweeping, mopping, utensils</v>
@@ -1007,7 +1068,7 @@
         <v>6 AM – 10 AM</v>
       </c>
       <c r="E15" t="str">
-        <v>+91 90210 33002</v>
+        <v/>
       </c>
       <c r="F15" t="str">
         <v>Also irons clothes on request</v>
@@ -1027,7 +1088,7 @@
         <v>11 AM – 2 PM</v>
       </c>
       <c r="E16" t="str">
-        <v>+91 90210 33005</v>
+        <v/>
       </c>
       <c r="F16" t="str">
         <v>Vegetarian, two meals a day</v>
@@ -1035,7 +1096,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Imran Shaikh</v>
+        <v>ganesh raju</v>
       </c>
       <c r="B17" t="str">
         <v>Car Cleaning</v>
@@ -1047,7 +1108,7 @@
         <v>6 AM – 9 AM</v>
       </c>
       <c r="E17" t="str">
-        <v>+91 90210 33006</v>
+        <v/>
       </c>
       <c r="F17" t="str">
         <v>Daily wash, interior weekly</v>
@@ -1067,7 +1128,7 @@
         <v>By appointment</v>
       </c>
       <c r="E18" t="str">
-        <v>+91 90210 33007</v>
+        <v/>
       </c>
       <c r="F18" t="str">
         <v>Local trips, holds a valid licence</v>
@@ -1087,7 +1148,7 @@
         <v>Flexible</v>
       </c>
       <c r="E19" t="str">
-        <v>+91 90210 33008</v>
+        <v/>
       </c>
       <c r="F19" t="str">
         <v>Experienced with toddlers</v>
@@ -1102,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:R21"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1110,6 +1171,18 @@
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,497 +1204,1173 @@
       <c r="F1" t="str">
         <v>Type</v>
       </c>
+      <c r="G1" t="str">
+        <v>Blood Group</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Emergency Contact</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Vehicle No</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Vehicle Type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Parking Slot</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Profession</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Language</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Occupants</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Pets</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Owner Name</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Owner Phone</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Owner Address</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Anil Kulkarni</v>
+        <v>Test Name</v>
       </c>
       <c r="B2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="C2" t="str">
-        <v>A-101</v>
+        <v>10</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>9876543210</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>abc@xyz.com</v>
       </c>
       <c r="F2" t="str">
+        <v>owner</v>
+      </c>
+      <c r="G2" t="str">
+        <v>O+</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Relative name, +91 98220 11111</v>
+      </c>
+      <c r="I2" t="str">
+        <v>MH-09-AB-1234</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Car</v>
+      </c>
+      <c r="K2" t="str">
+        <v>P-12</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Doctor</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Marathi</v>
+      </c>
+      <c r="N2" t="str">
+        <v>4</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Priya Raghavan</v>
+        <v>Test Name - Tenant</v>
       </c>
       <c r="B3" t="str">
         <v>A</v>
       </c>
       <c r="C3" t="str">
-        <v>A-202</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>9876543210</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>abc@xyz.com</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>tenant</v>
+      </c>
+      <c r="G3" t="str">
+        <v>A+</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>MH-09-CD-5678</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Two-wheeler</v>
+      </c>
+      <c r="K3" t="str">
+        <v>P-31</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O3" t="str">
+        <v>1 cat</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Flat Owner Name</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>+91 98200 44002</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Owner's address, city</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Imran Shaikh</v>
+        <v>Narendrakumar heda</v>
       </c>
       <c r="B4" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="C4" t="str">
-        <v>A-305</v>
+        <v>11</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>8793109590</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Kavita Joshi</v>
+        <v>Bhavesh Rajeshkumar Sarda</v>
       </c>
       <c r="B5" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="C5" t="str">
-        <v>A-506</v>
+        <v>B-2</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>8482996010</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>bhaveshsarda2004@gmail.com</v>
       </c>
       <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Rohan Bhatia</v>
+        <v>Sagar Agarwal</v>
       </c>
       <c r="B6" t="str">
         <v>A</v>
       </c>
       <c r="C6" t="str">
-        <v>A-608</v>
+        <v>A - 2</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>7350665037</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>agarwalsagar016@gmail.com</v>
       </c>
       <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Rajesh Menon</v>
+        <v>Rahul Pareek</v>
       </c>
       <c r="B7" t="str">
         <v>B</v>
       </c>
       <c r="C7" t="str">
-        <v>B-201</v>
+        <v>9</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>9156704040</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>rahulpareek3366@gmail.com</v>
       </c>
       <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Deepa Chatterjee</v>
+        <v>Shrihari Narayan Makote</v>
       </c>
       <c r="B8" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="C8" t="str">
-        <v>B-302</v>
+        <v>12</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>9922497427</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>shriharimakote70@gmail.com</v>
       </c>
       <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Vikram Rathore</v>
+        <v>Ramdev Rathi</v>
       </c>
       <c r="B9" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="C9" t="str">
-        <v>B-403</v>
+        <v>C2-C3</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>9422423985</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nisha Patel</v>
+        <v>Pradeep Jhunjhunwala</v>
       </c>
       <c r="B10" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="C10" t="str">
-        <v>B-505</v>
+        <v>A-10</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>9922114900</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>cool16yash@gmail.com</v>
       </c>
       <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Arjun Sethi</v>
+        <v>Harishkumar Bharatkumar</v>
       </c>
       <c r="B11" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="C11" t="str">
-        <v>B-707</v>
+        <v>C-14</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>7019426263</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Suresh Pillai</v>
+        <v>Laxmi kant balkrishan malpani</v>
       </c>
       <c r="B12" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="C12" t="str">
-        <v>C-102</v>
+        <v>A/1</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>9372281026</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ayesha Khan</v>
+        <v>AMIT KUMAR</v>
       </c>
       <c r="B13" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="C13" t="str">
-        <v>C-304</v>
+        <v>13</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>9970962853</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>Tenant</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v>NARENDRA SANGHVI</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>8999393126</v>
+      </c>
+      <c r="R13" t="str">
+        <v>Dhanya galli</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Gopal Verma</v>
+        <v>Shripad Pandit Deshpande</v>
       </c>
       <c r="B14" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="C14" t="str">
-        <v>C-405</v>
+        <v>B-8</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>9422427667</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Lakshmi Subramanian</v>
+        <v>Vishnu Kumar Malu</v>
       </c>
       <c r="B15" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="C15" t="str">
-        <v>C-506</v>
+        <v>B 3</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>8830301347</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Tanvi Mehta</v>
+        <v>Saurabh Khombare</v>
       </c>
       <c r="B16" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="C16" t="str">
-        <v>C-608</v>
+        <v>B-19</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>9482856848</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Narendrakumar heda</v>
+        <v>Omnarayan Pannalal jaju</v>
       </c>
       <c r="B17" t="str">
         <v>B</v>
       </c>
       <c r="C17" t="str">
-        <v>11</v>
+        <v>B-7</v>
       </c>
       <c r="D17" t="str">
-        <v>8793109590</v>
+        <v>9423815210</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>jajuop1960@gmail.com</v>
       </c>
       <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Bhavesh Rajeshkumar Sarda</v>
+        <v>Abhijeet Uday Altekar</v>
       </c>
       <c r="B18" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="C18" t="str">
-        <v>B-2</v>
+        <v>A-17</v>
       </c>
       <c r="D18" t="str">
-        <v>8482996010</v>
+        <v>8698117111</v>
       </c>
       <c r="E18" t="str">
-        <v>bhaveshsarda2004@gmail.com</v>
+        <v>abhijeet.altekar@gmail.com</v>
       </c>
       <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sagar Agarwal</v>
+        <v>Anil Akiwate</v>
       </c>
       <c r="B19" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="C19" t="str">
-        <v>A - 2</v>
+        <v>C-12</v>
       </c>
       <c r="D19" t="str">
-        <v>7350665037</v>
+        <v>8379805687</v>
       </c>
       <c r="E19" t="str">
-        <v>agarwalsagar016@gmail.com</v>
+        <v>anilakiwate@gmail.com</v>
       </c>
       <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Rahul Pareek</v>
+        <v>Nilesh Koshti</v>
       </c>
       <c r="B20" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="C20" t="str">
-        <v>9</v>
+        <v>D-6</v>
       </c>
       <c r="D20" t="str">
-        <v>9156704040</v>
+        <v>8600204473</v>
       </c>
       <c r="E20" t="str">
-        <v>rahulpareek3366@gmail.com</v>
+        <v>nilesh2348@gmail.com</v>
       </c>
       <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Shrihari Narayan Makote</v>
+        <v>Madhavnarayan Rathi</v>
       </c>
       <c r="B21" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="C21" t="str">
-        <v>12</v>
+        <v>B-4</v>
       </c>
       <c r="D21" t="str">
-        <v>9922497427</v>
+        <v>8830149385</v>
       </c>
       <c r="E21" t="str">
-        <v>shriharimakote70@gmail.com</v>
+        <v>mrathi44@gmail.com</v>
       </c>
       <c r="F21" t="str">
         <v/>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Ramdev Rathi</v>
-      </c>
-      <c r="B22" t="str">
-        <v>C</v>
-      </c>
-      <c r="C22" t="str">
-        <v>C2-C3</v>
-      </c>
-      <c r="D22" t="str">
-        <v>9422423985</v>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Pradeep Jhunjhunwala</v>
-      </c>
-      <c r="B23" t="str">
-        <v>A</v>
-      </c>
-      <c r="C23" t="str">
-        <v>A-10</v>
-      </c>
-      <c r="D23" t="str">
-        <v>9922114900</v>
-      </c>
-      <c r="E23" t="str">
-        <v>cool16yash@gmail.com</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Harishkumar Bharatkumar</v>
-      </c>
-      <c r="B24" t="str">
-        <v>C</v>
-      </c>
-      <c r="C24" t="str">
-        <v>C-14</v>
-      </c>
-      <c r="D24" t="str">
-        <v>7019426263</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Laxmi kant balkrishan malpani</v>
-      </c>
-      <c r="B25" t="str">
-        <v>A</v>
-      </c>
-      <c r="C25" t="str">
-        <v>A/1</v>
-      </c>
-      <c r="D25" t="str">
-        <v>9372281026</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1649,75 +2398,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Society Bye-Laws (2024 revision)</v>
+        <v>Society Bye-Laws</v>
       </c>
       <c r="B2" t="str">
         <v>Governance</v>
       </c>
       <c r="C2" t="str">
-        <v>materials/Society_Bye_Laws_2024.pdf</v>
+        <v>materials/Society_Bye_Laws.pdf</v>
       </c>
       <c r="D2" t="str">
-        <v>2024-06-18</v>
+        <v>2026-01-01</v>
       </c>
       <c r="E2" t="str">
-        <v>Registered bye-laws currently in force</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>AGM Minutes 2025</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Governance</v>
-      </c>
-      <c r="C3" t="str">
-        <v>materials/AGM_Minutes_2025.pdf</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2025-09-20</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Annual general meeting, 14 September 2025</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Maintenance &amp; Water Circular</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Circulars</v>
-      </c>
-      <c r="C4" t="str">
-        <v>materials/Maintenance_Circular_Aug_2025.pdf</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2025-08-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Payment dates and revised water timings</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Flat Transfer Application Form</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Forms</v>
-      </c>
-      <c r="C5" t="str">
-        <v>materials/Flat_Transfer_Form.pdf</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2024-11-02</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Submit to the society office with enclosures</v>
+        <v>Upload the file in the admin panel; it fills this row for you</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1891,4 +2589,317 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Person</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Relation</v>
+      </c>
+      <c r="D1" t="str">
+        <v>DOB</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Medical Notes</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Elderly or alone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Lease Ends</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Police Verification</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A-101</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Example Owner</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1979-04-12</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Diabetic</v>
+      </c>
+      <c r="F2" t="str">
+        <v>No</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>B-403</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Example Tenant</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="D3" t="str">
+        <v>1990-08-30</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>No</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2027-03-31</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Done 2026-02-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Topic</v>
+      </c>
+      <c r="B1" t="str">
+        <v>English</v>
+      </c>
+      <c r="C1" t="str">
+        <v>हिंदी</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sheets</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Every sheet tab becomes a section on the website, in this order. Add a tab, get a section.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>हर शीट वेबसाइट पर एक अनुभाग बन जाती है। नई शीट जोड़ें, नया अनुभाग बनेगा।</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>About</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Not a section — it fills the page header and holds the settings below.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>यह अनुभाग नहीं है — इससे पेज का शीर्षक और सेटिंग्स बनती हैं।</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Emergency</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Any tab whose name contains "emerg" shows in red in the sidebar.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>जिस शीट के नाम में "emerg" हो, वह साइडबार में लाल रंग में दिखेगी।</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Any tab with a File column becomes the documents panel.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>जिस शीट में File कॉलम हो, वह दस्तावेज़ पैनल बन जाएगी।</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Private data</v>
+      </c>
+      <c r="B6" t="str">
+        <v>A sheet or column starting with _ is stored but never shown on the site. Use it for dates of birth.</v>
+      </c>
+      <c r="C6" t="str">
+        <v>_ से शुरू होने वाली शीट या कॉलम वेबसाइट पर कभी नहीं दिखेंगे। जन्मतिथि आदि के लिए इसका उपयोग करें।</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Name column</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Name, Service, Person or Title becomes the card heading.</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Name, Service, Person या Title कार्ड का शीर्षक बनता है।</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Phone column</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Phone, Mobile, Contact No or Cell becomes a call button.</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Phone, Mobile, Contact No या Cell कॉल बटन बन जाता है।</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Role column</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Role, Designation, Post or Type shows as the small label.</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Role, Designation, Post या Type छोटे लेबल के रूप में दिखता है।</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Charges column</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Charges, Rate, Fee or Price shows as a gold badge.</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Charges, Rate, Fee या Price सुनहरे बैज में दिखता है।</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Owner columns</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Owner Name / Owner Phone / Owner Address show behind an "Owner details" button, for tenanted flats.</v>
+      </c>
+      <c r="C11" t="str">
+        <v>किरायेदार वाले फ्लैट के लिए मकान मालिक का विवरण एक बटन के पीछे दिखता है।</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Phone format</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Format phone columns as TEXT in Excel, or it will drop the + and leading zeros.</v>
+      </c>
+      <c r="C12" t="str">
+        <v>फ़ोन कॉलम को Excel में TEXT फ़ॉर्मैट रखें, वरना + और शुरुआती शून्य हट जाएँगे।</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Add "Hindi: &lt;sheet name&gt;" rows in About to translate section names. Values you type are shown as-is, so Hindi names work anywhere.</v>
+      </c>
+      <c r="C13" t="str">
+        <v>अनुभागों के हिंदी नाम About शीट में "Hindi: &lt;नाम&gt;" पंक्ति से जोड़ें। आपके लिखे मान जैसे हैं वैसे दिखते हैं।</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Blood group</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Shown as a red badge on the card. Use a dropdown in your form so you do not collect "o positive" and "O +ve".</v>
+      </c>
+      <c r="C14" t="str">
+        <v>कार्ड पर लाल बैज में दिखता है। फ़ॉर्म में ड्रॉपडाउन रखें।</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Optional fields</v>
+      </c>
+      <c r="B15" t="str">
+        <v>The first two extra columns show on the card; the rest fold behind a More details button. Search still finds them and opens the card.</v>
+      </c>
+      <c r="C15" t="str">
+        <v>पहले दो अतिरिक्त कॉलम कार्ड पर दिखते हैं, बाक़ी "More details" के पीछे। खोज उन्हें भी ढूँढ लेती है।</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Owner columns</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Fill Owner Name / Owner Phone / Owner Address only for tenanted flats. They appear behind an Owner details button; leave blank and nothing is shown.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>किरायेदार वाले फ्लैट के लिए ही भरें। खाली छोड़ने पर कुछ नहीं दिखेगा।</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>_Private sheet</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Dates of birth, medical notes, lease dates and police verification live here. The leading underscore keeps the sheet off the website entirely.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>जन्मतिथि, चिकित्सा जानकारी आदि यहाँ रखें। यह शीट वेबसाइट पर कभी नहीं दिखती।</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Examples</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Delete the example rows before publishing.</v>
+      </c>
+      <c r="C18" t="str">
+        <v>प्रकाशित करने से पहले उदाहरण पंक्तियाँ हटा दें।</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -9,9 +9,8 @@
     <sheet name="Services &amp; Help" sheetId="4" r:id="rId4"/>
     <sheet name="Residents" sheetId="5" r:id="rId5"/>
     <sheet name="Documents" sheetId="6" r:id="rId6"/>
-    <sheet name="Services" sheetId="7" r:id="rId7"/>
-    <sheet name="_Private" sheetId="8" r:id="rId8"/>
-    <sheet name="_Read me" sheetId="9" r:id="rId9"/>
+    <sheet name="_Private" sheetId="7" r:id="rId7"/>
+    <sheet name="_Read me" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -406,11 +405,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -609,13 +603,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -678,12 +665,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -765,14 +746,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F19"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1164,26 +1137,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R21"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="21.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="13.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" customWidth="1"/>
-    <col min="18" max="18" width="17.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2371,13 +2324,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2422,188 +2368,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Service</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Contact</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Plumber</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Electrician</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Lift Technician</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Pest Control</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Housekeeping</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Water Tanker</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Electricity Board</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Gas Agency</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Society Manager</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="23.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2690,14 +2455,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/data.xlsx
+++ b/data.xlsx
@@ -404,7 +404,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -496,43 +501,43 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Confidential Notice</v>
+        <v>Theme</v>
       </c>
       <c r="B9" t="str">
-        <v>Please do not forward this link or share these details with anyone outside the society.</v>
+        <v>Paper</v>
       </c>
       <c r="C9" t="str">
-        <v>ऊपर दिखने वाली चेतावनी (अंग्रेज़ी)</v>
+        <v>navy, forest, plum, slate, sunset, ocean, paper</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Confidential HI</v>
+        <v>Hindi: Committee</v>
       </c>
       <c r="B10" t="str">
-        <v>कृपया यह लिंक या विवरण सोसाइटी के बाहर किसी के साथ साझा न करें।</v>
+        <v>समिति</v>
       </c>
       <c r="C10" t="str">
-        <v>वही चेतावनी हिंदी में</v>
+        <v>हिंदी में अनुभाग का नाम</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Theme</v>
+        <v>Hindi: Emergency</v>
       </c>
       <c r="B11" t="str">
-        <v>Paper</v>
+        <v>आपातकालीन संपर्क</v>
       </c>
       <c r="C11" t="str">
-        <v>navy, forest, plum, slate, sunset, ocean, paper</v>
+        <v>हिंदी में अनुभाग का नाम</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Hindi: Committee</v>
+        <v>Hindi: Services &amp; Help</v>
       </c>
       <c r="B12" t="str">
-        <v>समिति</v>
+        <v>सेवाएँ और सहायता</v>
       </c>
       <c r="C12" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -540,10 +545,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hindi: Emergency</v>
+        <v>Hindi: Residents</v>
       </c>
       <c r="B13" t="str">
-        <v>आपातकालीन संपर्क</v>
+        <v>निवासी</v>
       </c>
       <c r="C13" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -551,10 +556,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Hindi: Services &amp; Help</v>
+        <v>Hindi: Documents</v>
       </c>
       <c r="B14" t="str">
-        <v>सेवाएँ और सहायता</v>
+        <v>दस्तावेज़</v>
       </c>
       <c r="C14" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -562,40 +567,18 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Hindi: Residents</v>
+        <v>Note: Services &amp; Help</v>
       </c>
       <c r="B15" t="str">
-        <v>निवासी</v>
+        <v>These contacts are collected from members. They have not been verified or endorsed. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
       </c>
       <c r="C15" t="str">
-        <v>हिंदी में अनुभाग का नाम</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Hindi: Documents</v>
-      </c>
-      <c r="B16" t="str">
-        <v>दस्तावेज़</v>
-      </c>
-      <c r="C16" t="str">
-        <v>हिंदी में अनुभाग का नाम</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Note: Services &amp; Help</v>
-      </c>
-      <c r="B17" t="str">
-        <v>These contacts are collected from members. They have not been verified or endorsed. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
-      </c>
-      <c r="C17" t="str">
         <v>उस अनुभाग के नीचे दिखने वाली चेतावनी</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -406,9 +406,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-    <col min="3" max="3" width="46.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,6 +586,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -648,6 +655,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -729,6 +742,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F19"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -752,42 +773,42 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Santosh Gupta</v>
+        <v>Rahul Shelar</v>
       </c>
       <c r="B2" t="str">
         <v>Plumber</v>
       </c>
       <c r="C2" t="str">
-        <v>₹100 / visit</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>8 AM – 8 PM, on call</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>9673020210</v>
       </c>
       <c r="F2" t="str">
-        <v>Parts charged separately</v>
+        <v>Plumbing solutions</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Naresh Bhoir</v>
+        <v>Ankush Mhetar</v>
       </c>
       <c r="B3" t="str">
         <v>Electrician</v>
       </c>
       <c r="C3" t="str">
-        <v>₹120 / visit</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>9 AM – 8 PM, on call</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>9309564191</v>
       </c>
       <c r="F3" t="str">
-        <v>Wiring, fans, MCB</v>
+        <v>Major and Minor electric works</v>
       </c>
     </row>
     <row r="4">
@@ -1120,6 +1141,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R21"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="17.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2307,6 +2348,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2352,6 +2400,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2441,6 +2499,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/data.xlsx
+++ b/data.xlsx
@@ -405,11 +405,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-    <col min="3" max="3" width="46.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1119,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1132,48 +1127,51 @@
         <v>Flat</v>
       </c>
       <c r="D1" t="str">
+        <v>Unit Type</v>
+      </c>
+      <c r="E1" t="str">
         <v>Phone</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Email</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Type</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Blood Group</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Emergency Contact</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Vehicle No</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Vehicle Type</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Parking Slot</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Profession</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Language</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Occupants</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Pets</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Owner Name</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Owner Phone</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Owner Address</v>
       </c>
     </row>
@@ -1188,41 +1186,41 @@
         <v>10</v>
       </c>
       <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
         <v>9876543210</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>abc@xyz.com</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>owner</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>O+</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Relative name, +91 98220 11111</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>MH-09-AB-1234</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Car</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>P-12</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>Doctor</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>Marathi</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>4</v>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
       <c r="P2" t="str">
         <v/>
       </c>
@@ -1230,6 +1228,9 @@
         <v/>
       </c>
       <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
         <v/>
       </c>
     </row>
@@ -1244,48 +1245,51 @@
         <v>2</v>
       </c>
       <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
         <v>9876543210</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>abc@xyz.com</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>tenant</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>A+</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
       <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v>MH-09-CD-5678</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>Two-wheeler</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>P-31</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>Teacher</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>Hindi</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>2</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>1 cat</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>Flat Owner Name</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>+91 98200 44002</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <v>Owner's address, city</v>
       </c>
     </row>
@@ -1300,11 +1304,11 @@
         <v>11</v>
       </c>
       <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
         <v>8793109590</v>
       </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
       <c r="F4" t="str">
         <v/>
       </c>
@@ -1342,6 +1346,9 @@
         <v/>
       </c>
       <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
         <v/>
       </c>
     </row>
@@ -1356,14 +1363,14 @@
         <v>B-2</v>
       </c>
       <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
         <v>8482996010</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>bhaveshsarda2004@gmail.com</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
       <c r="G5" t="str">
         <v/>
       </c>
@@ -1398,6 +1405,9 @@
         <v/>
       </c>
       <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
         <v/>
       </c>
     </row>
@@ -1412,14 +1422,14 @@
         <v>A - 2</v>
       </c>
       <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
         <v>7350665037</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>agarwalsagar016@gmail.com</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
       <c r="G6" t="str">
         <v/>
       </c>
@@ -1454,6 +1464,9 @@
         <v/>
       </c>
       <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
         <v/>
       </c>
     </row>
@@ -1468,14 +1481,14 @@
         <v>9</v>
       </c>
       <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
         <v>9156704040</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>rahulpareek3366@gmail.com</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
       <c r="G7" t="str">
         <v/>
       </c>
@@ -1510,6 +1523,9 @@
         <v/>
       </c>
       <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
         <v/>
       </c>
     </row>
@@ -1524,14 +1540,14 @@
         <v>12</v>
       </c>
       <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
         <v>9922497427</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <v>shriharimakote70@gmail.com</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
       <c r="G8" t="str">
         <v/>
       </c>
@@ -1566,6 +1582,9 @@
         <v/>
       </c>
       <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
         <v/>
       </c>
     </row>
@@ -1580,11 +1599,11 @@
         <v>C2-C3</v>
       </c>
       <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
         <v>9422423985</v>
       </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
       <c r="F9" t="str">
         <v/>
       </c>
@@ -1622,6 +1641,9 @@
         <v/>
       </c>
       <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
         <v/>
       </c>
     </row>
@@ -1636,14 +1658,14 @@
         <v>A-10</v>
       </c>
       <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
         <v>9922114900</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>cool16yash@gmail.com</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
       <c r="G10" t="str">
         <v/>
       </c>
@@ -1678,6 +1700,9 @@
         <v/>
       </c>
       <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
         <v/>
       </c>
     </row>
@@ -1692,11 +1717,11 @@
         <v>C-14</v>
       </c>
       <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
         <v>7019426263</v>
       </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
       <c r="F11" t="str">
         <v/>
       </c>
@@ -1734,6 +1759,9 @@
         <v/>
       </c>
       <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
         <v/>
       </c>
     </row>
@@ -1748,11 +1776,11 @@
         <v>A/1</v>
       </c>
       <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
         <v>9372281026</v>
       </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
       <c r="F12" t="str">
         <v/>
       </c>
@@ -1790,6 +1818,9 @@
         <v/>
       </c>
       <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
         <v/>
       </c>
     </row>
@@ -1804,17 +1835,17 @@
         <v>13</v>
       </c>
       <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
         <v>9970962853</v>
       </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
       <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
         <v>Tenant</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
       <c r="H13" t="str">
         <v/>
       </c>
@@ -1840,12 +1871,15 @@
         <v/>
       </c>
       <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
         <v>NARENDRA SANGHVI</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="R13" t="str">
         <v>8999393126</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
         <v>Dhanya galli</v>
       </c>
     </row>
@@ -1860,11 +1894,11 @@
         <v>B-8</v>
       </c>
       <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
         <v>9422427667</v>
       </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
       <c r="F14" t="str">
         <v/>
       </c>
@@ -1902,6 +1936,9 @@
         <v/>
       </c>
       <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
         <v/>
       </c>
     </row>
@@ -1916,11 +1953,11 @@
         <v>B 3</v>
       </c>
       <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
         <v>8830301347</v>
       </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
       <c r="F15" t="str">
         <v/>
       </c>
@@ -1958,6 +1995,9 @@
         <v/>
       </c>
       <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
         <v/>
       </c>
     </row>
@@ -1972,11 +2012,11 @@
         <v>B-19</v>
       </c>
       <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
         <v>9482856848</v>
       </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
       <c r="F16" t="str">
         <v/>
       </c>
@@ -2014,6 +2054,9 @@
         <v/>
       </c>
       <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
         <v/>
       </c>
     </row>
@@ -2028,14 +2071,14 @@
         <v>B-7</v>
       </c>
       <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
         <v>9423815210</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
         <v>jajuop1960@gmail.com</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
       <c r="G17" t="str">
         <v/>
       </c>
@@ -2070,6 +2113,9 @@
         <v/>
       </c>
       <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
         <v/>
       </c>
     </row>
@@ -2084,14 +2130,14 @@
         <v>A-17</v>
       </c>
       <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
         <v>8698117111</v>
       </c>
-      <c r="E18" t="str">
+      <c r="F18" t="str">
         <v>abhijeet.altekar@gmail.com</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
       <c r="G18" t="str">
         <v/>
       </c>
@@ -2126,6 +2172,9 @@
         <v/>
       </c>
       <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
         <v/>
       </c>
     </row>
@@ -2140,14 +2189,14 @@
         <v>C-12</v>
       </c>
       <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
         <v>8379805687</v>
       </c>
-      <c r="E19" t="str">
+      <c r="F19" t="str">
         <v>anilakiwate@gmail.com</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
       <c r="G19" t="str">
         <v/>
       </c>
@@ -2182,6 +2231,9 @@
         <v/>
       </c>
       <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
         <v/>
       </c>
     </row>
@@ -2196,14 +2248,14 @@
         <v>D-6</v>
       </c>
       <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
         <v>8600204473</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
         <v>nilesh2348@gmail.com</v>
       </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
       <c r="G20" t="str">
         <v/>
       </c>
@@ -2238,6 +2290,9 @@
         <v/>
       </c>
       <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
         <v/>
       </c>
     </row>
@@ -2252,14 +2307,14 @@
         <v>B-4</v>
       </c>
       <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
         <v>8830149385</v>
       </c>
-      <c r="E21" t="str">
+      <c r="F21" t="str">
         <v>mrathi44@gmail.com</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
       <c r="G21" t="str">
         <v/>
       </c>
@@ -2294,12 +2349,15 @@
         <v/>
       </c>
       <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2440,7 +2498,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2640,9 +2698,20 @@
         <v>प्रकाशित करने से पहले उदाहरण पंक्तियाँ हटा दें।</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Unit Type</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Flat, Row House, Shop or Bungalow. Fill this in wherever a wing and number repeat — a flat B-11 and a row house B-11 are two different homes, and without this they look identical on the page and would share one access code. Leave it blank if there is no ambiguity.</v>
+      </c>
+      <c r="C19" t="str">
+        <v>फ्लैट, रो हाउस, दुकान या बंगला। जहाँ विंग और नंबर एक जैसे हों वहाँ यह भरें — फ्लैट B-11 और रो हाउस B-11 दो अलग घर हैं। ज़रूरत न हो तो खाली छोड़ दें।</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -3,14 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Committee" sheetId="2" r:id="rId2"/>
-    <sheet name="Emergency" sheetId="3" r:id="rId3"/>
-    <sheet name="Services &amp; Help" sheetId="4" r:id="rId4"/>
-    <sheet name="Residents" sheetId="5" r:id="rId5"/>
-    <sheet name="Documents" sheetId="6" r:id="rId6"/>
-    <sheet name="_Private" sheetId="7" r:id="rId7"/>
-    <sheet name="_Read me" sheetId="8" r:id="rId8"/>
+    <sheet name="Notices" sheetId="1" r:id="rId1"/>
+    <sheet name="About" sheetId="2" r:id="rId2"/>
+    <sheet name="Committee" sheetId="3" r:id="rId3"/>
+    <sheet name="Emergency" sheetId="4" r:id="rId4"/>
+    <sheet name="Services &amp; Help" sheetId="5" r:id="rId5"/>
+    <sheet name="Residents" sheetId="6" r:id="rId6"/>
+    <sheet name="Documents" sheetId="7" r:id="rId7"/>
+    <sheet name="_Private" sheetId="8" r:id="rId8"/>
+    <sheet name="_Read me" sheetId="9" r:id="rId9"/>
+    <sheet name="Local Numbers" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -404,6 +406,347 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Details</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Pinned</v>
+      </c>
+      <c r="F1" t="str">
+        <v>File</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>01/09/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Annual General Meeting — Sunday 20 September, 10 AM</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">The AGM will be held in the society compound. Agenda: audited accounts for 2025-26, maintenance revision, lift AMC renewal, and election of the new committee.
+Please attend. If you cannot, send your written consent with a neighbour.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Meeting</v>
+      </c>
+      <c r="E2" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>28/08/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Water tank cleaning — Thursday 3 September</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Both overhead tanks will be cleaned from 9 AM. Water supply will be off between 9 AM and 2 PM. Please store what you need the night before.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Maintenance</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>10/08/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Maintenance for July–September is due</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Kindly pay by the 15th. Bank and UPI details are on the notice board and with the treasurer.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Payment</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D17"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Service</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Contact</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Emergency (all services)</v>
+      </c>
+      <c r="B2" t="str">
+        <v>National</v>
+      </c>
+      <c r="C2" t="str">
+        <v>112</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Police, fire and ambulance from one number</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Ambulance</v>
+      </c>
+      <c r="B3" t="str">
+        <v>National</v>
+      </c>
+      <c r="C3" t="str">
+        <v>108</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Fire</v>
+      </c>
+      <c r="B4" t="str">
+        <v>National</v>
+      </c>
+      <c r="C4" t="str">
+        <v>101</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Police</v>
+      </c>
+      <c r="B5" t="str">
+        <v>National</v>
+      </c>
+      <c r="C5" t="str">
+        <v>100</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Electricity complaint (MSEDCL)</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Toll free</v>
+      </c>
+      <c r="C6" t="str">
+        <v>1912</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Also 1800-233-3435</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Women's helpline</v>
+      </c>
+      <c r="B7" t="str">
+        <v>National</v>
+      </c>
+      <c r="C7" t="str">
+        <v>181</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Childline</v>
+      </c>
+      <c r="B8" t="str">
+        <v>National</v>
+      </c>
+      <c r="C8" t="str">
+        <v>1098</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Senior citizen helpline</v>
+      </c>
+      <c r="B9" t="str">
+        <v>National</v>
+      </c>
+      <c r="C9" t="str">
+        <v>14567</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Municipal council office</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>FILL IN — Ichalkaranji</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Municipal water supply</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>FILL IN</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Nearest hospital</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>FILL IN</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Nearest chemist (24 hr)</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>FILL IN</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Gas agency</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>FILL IN — consumer number helps</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Milk delivery</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>FILL IN</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Newspaper</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>FILL IN</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Garbage collection</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>FILL IN</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <sheetData>
@@ -640,7 +983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
   <sheetData>
@@ -721,7 +1064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F19"/>
   <sheetData>
@@ -1112,7 +1455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S21"/>
   <sheetData>
@@ -2362,7 +2705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetData>
@@ -2407,7 +2750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <sheetData>
@@ -2496,9 +2839,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2709,9 +3052,31 @@
         <v>फ्लैट, रो हाउस, दुकान या बंगला। जहाँ विंग और नंबर एक जैसे हों वहाँ यह भरें — फ्लैट B-11 और रो हाउस B-11 दो अलग घर हैं। ज़रूरत न हो तो खाली छोड़ दें।</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Notices</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Put the newest notice anywhere in the sheet — the page sorts by Date itself, newest first, and marks anything from the last 14 days as New. Put yes in the Pinned column to keep a notice at the top regardless of date (use it for the AGM, then clear it). Dates can be written 25/08/2026, 25 Aug 2026 or 2026-08-25. The Notices section always appears first on the page.</v>
+      </c>
+      <c r="C20" t="str">
+        <v>सबसे नई सूचना कहीं भी लिखें — पेज खुद तारीख से क्रम लगाता है और पिछले 14 दिन की सूचना पर New दिखाता है। किसी सूचना को सबसे ऊपर रखना हो तो Pinned में yes लिखें।</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Local Numbers</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Everyday numbers that are not emergencies: municipal office, gas agency, milk, newspaper, chemist. Rows marked FILL IN still need the local number — they were left blank rather than guessed.</v>
+      </c>
+      <c r="C21" t="str">
+        <v>रोज़मर्रा के नंबर: नगरपालिका, गैस एजेंसी, दूध, अख़बार, दवाई की दुकान। FILL IN लिखी पंक्तियों में स्थानीय नंबर भरना बाकी है।</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -3057,7 +3057,7 @@
         <v>Notices</v>
       </c>
       <c r="B20" t="str">
-        <v>Put the newest notice anywhere in the sheet — the page sorts by Date itself, newest first, and marks anything from the last 14 days as New. Put yes in the Pinned column to keep a notice at the top regardless of date (use it for the AGM, then clear it). Dates can be written 25/08/2026, 25 Aug 2026 or 2026-08-25. The Notices section always appears first on the page.</v>
+        <v>Put the newest notice anywhere in the sheet — the page sorts by Date itself, newest first, and marks anything from the last 14 days as New. Put yes in the Pinned column to keep a notice at the top regardless of date (use it for the AGM, then clear it). Dates can be written 25/08/2026, 25 Aug 2026 or 2026-08-25. The Notices section sits at the bottom of the page, below the contact sections.</v>
       </c>
       <c r="C20" t="str">
         <v>सबसे नई सूचना कहीं भी लिखें — पेज खुद तारीख से क्रम लगाता है और पिछले 14 दिन की सूचना पर New दिखाता है। किसी सूचना को सबसे ऊपर रखना हो तो Pinned में yes लिखें।</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1066,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1076,15 +1076,18 @@
         <v>Role</v>
       </c>
       <c r="C1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="D1" t="str">
         <v>Charges</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Timings</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Phone</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -1096,15 +1099,18 @@
         <v>Plumber</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Repairs &amp; Maintenance</v>
       </c>
       <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
         <v>8 AM – 8 PM, on call</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>9673020210</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Plumbing solutions</v>
       </c>
     </row>
@@ -1116,15 +1122,18 @@
         <v>Electrician</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Repairs &amp; Maintenance</v>
       </c>
       <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
         <v>9 AM – 8 PM, on call</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>9309564191</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Major and Minor electric works</v>
       </c>
     </row>
@@ -1136,15 +1145,18 @@
         <v>Carpenter</v>
       </c>
       <c r="C4" t="str">
+        <v>Repairs &amp; Maintenance</v>
+      </c>
+      <c r="D4" t="str">
         <v>₹150 / visit</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>On call</v>
       </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
         <v>Furniture repair and fittings</v>
       </c>
     </row>
@@ -1156,15 +1168,18 @@
         <v>Lift Technician</v>
       </c>
       <c r="C5" t="str">
+        <v>Building Services</v>
+      </c>
+      <c r="D5" t="str">
         <v>Society AMC</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>4-hour response</v>
       </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
       <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
         <v>Report faults to the manager first</v>
       </c>
     </row>
@@ -1176,15 +1191,18 @@
         <v>Pest Control</v>
       </c>
       <c r="C6" t="str">
+        <v>Building Services</v>
+      </c>
+      <c r="D6" t="str">
         <v>₹1,200 / flat</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>By appointment</v>
       </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
       <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
         <v>Quarterly society drive is free</v>
       </c>
     </row>
@@ -1196,15 +1214,18 @@
         <v>Housekeeping</v>
       </c>
       <c r="C7" t="str">
+        <v>Building Services</v>
+      </c>
+      <c r="D7" t="str">
         <v>Society staff</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>6 AM – 2 PM</v>
       </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
       <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
         <v>Common areas and staircases</v>
       </c>
     </row>
@@ -1216,15 +1237,18 @@
         <v>Gardener</v>
       </c>
       <c r="C8" t="str">
+        <v>Building Services</v>
+      </c>
+      <c r="D8" t="str">
         <v>₹80 / visit</v>
       </c>
-      <c r="D8" t="str">
+      <c r="E8" t="str">
         <v>Tue &amp; Sat mornings</v>
       </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
       <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
         <v>Balcony and terrace plants</v>
       </c>
     </row>
@@ -1236,15 +1260,18 @@
         <v>Water Tanker</v>
       </c>
       <c r="C9" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D9" t="str">
         <v>₹900 / tanker</v>
       </c>
-      <c r="D9" t="str">
+      <c r="E9" t="str">
         <v>Same-day delivery</v>
       </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
       <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
         <v>10,000 litre tanker</v>
       </c>
     </row>
@@ -1256,15 +1283,18 @@
         <v>Electricity Board</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>Utilities</v>
       </c>
       <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
         <v>24x7 helpline</v>
       </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
       <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
         <v>Outages and meter faults</v>
       </c>
     </row>
@@ -1276,15 +1306,18 @@
         <v>Gas Agency</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>Utilities</v>
       </c>
       <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
         <v>24x7 for leaks</v>
       </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
       <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
         <v>Leak helpline 1800 22 9944</v>
       </c>
     </row>
@@ -1296,15 +1329,18 @@
         <v>Society Manager</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>Society Staff</v>
       </c>
       <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
         <v>Mon–Sat, 10 AM – 6 PM</v>
       </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
       <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
         <v>Maintenance bills, NOCs, complaints</v>
       </c>
     </row>
@@ -1316,15 +1352,18 @@
         <v>Accountant</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>Society Staff</v>
       </c>
       <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
         <v>Tue &amp; Thu, 4 PM – 7 PM</v>
       </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
       <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
         <v>Dues, receipts, statements</v>
       </c>
     </row>
@@ -1336,15 +1375,18 @@
         <v>Maid</v>
       </c>
       <c r="C14" t="str">
+        <v>Home Help</v>
+      </c>
+      <c r="D14" t="str">
         <v>₹50 / visit</v>
       </c>
-      <c r="D14" t="str">
+      <c r="E14" t="str">
         <v>7 AM – 11 AM</v>
       </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
       <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
         <v>Sweeping, mopping, utensils</v>
       </c>
     </row>
@@ -1356,15 +1398,18 @@
         <v>Maid</v>
       </c>
       <c r="C15" t="str">
+        <v>Home Help</v>
+      </c>
+      <c r="D15" t="str">
         <v>₹60 / visit</v>
       </c>
-      <c r="D15" t="str">
+      <c r="E15" t="str">
         <v>6 AM – 10 AM</v>
       </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
       <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
         <v>Also irons clothes on request</v>
       </c>
     </row>
@@ -1376,15 +1421,18 @@
         <v>Cook</v>
       </c>
       <c r="C16" t="str">
+        <v>Home Help</v>
+      </c>
+      <c r="D16" t="str">
         <v>₹2,500 / month</v>
       </c>
-      <c r="D16" t="str">
+      <c r="E16" t="str">
         <v>11 AM – 2 PM</v>
       </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
       <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
         <v>Vegetarian, two meals a day</v>
       </c>
     </row>
@@ -1396,15 +1444,18 @@
         <v>Car Cleaning</v>
       </c>
       <c r="C17" t="str">
+        <v>Home Help</v>
+      </c>
+      <c r="D17" t="str">
         <v>₹500 / month</v>
       </c>
-      <c r="D17" t="str">
+      <c r="E17" t="str">
         <v>6 AM – 9 AM</v>
       </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
       <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
         <v>Daily wash, interior weekly</v>
       </c>
     </row>
@@ -1416,15 +1467,18 @@
         <v>Driver</v>
       </c>
       <c r="C18" t="str">
+        <v>Home Help</v>
+      </c>
+      <c r="D18" t="str">
         <v>₹300 / trip</v>
       </c>
-      <c r="D18" t="str">
+      <c r="E18" t="str">
         <v>By appointment</v>
       </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
       <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
         <v>Local trips, holds a valid licence</v>
       </c>
     </row>
@@ -1436,21 +1490,24 @@
         <v>Baby Sitter</v>
       </c>
       <c r="C19" t="str">
+        <v>Home Help</v>
+      </c>
+      <c r="D19" t="str">
         <v>₹150 / hour</v>
       </c>
-      <c r="D19" t="str">
+      <c r="E19" t="str">
         <v>Flexible</v>
       </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
       <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
         <v>Experienced with toddlers</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2841,7 +2898,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3074,9 +3131,20 @@
         <v>रोज़मर्रा के नंबर: नगरपालिका, गैस एजेंसी, दूध, अख़बार, दवाई की दुकान। FILL IN लिखी पंक्तियों में स्थानीय नंबर भरना बाकी है।</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Grouping</v>
+      </c>
+      <c r="B22" t="str">
+        <v>A section with 6 or more rows splits itself into groups, with a row of filter chips at the top. It picks the column by meaning — Block or Wing first, then Category, then Role. A column with a different value in almost every row is skipped, because that is a list with headings, not a grouping. To choose it yourself put a row in About: Field 'Group: Residents', Value 'Block'. Value 'none' turns grouping off for that sheet.</v>
+      </c>
+      <c r="C22" t="str">
+        <v>6 या अधिक पंक्तियों वाला अनुभाग अपने आप समूहों में बँट जाता है। स्तंभ अर्थ से चुना जाता है — पहले Block/Wing, फिर Category, फिर Role। खुद चुनना हो तो About में 'Group: Residents' = 'Block' लिखें; 'none' से समूह बंद हो जाएगा।</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -747,7 +747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -914,9 +914,31 @@
         <v>उस अनुभाग के नीचे दिखने वाली चेतावनी</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Services Page Title</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Local Services &amp; Help</v>
+      </c>
+      <c r="C16" t="str">
+        <v>सार्वजनिक सेवा पेज का शीर्षक — इसमें सोसाइटी का नाम न डालें</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Services Page Tagline</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Plumbers, electricians, help at home — numbers collected by neighbours.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>उस पेज की उपशीर्षक पंक्ति</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -13,6 +13,7 @@
     <sheet name="_Private" sheetId="8" r:id="rId8"/>
     <sheet name="_Read me" sheetId="9" r:id="rId9"/>
     <sheet name="Local Numbers" sheetId="10" r:id="rId10"/>
+    <sheet name="_Town Services" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -745,9 +746,66 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Role</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Charges</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Timings</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -936,9 +994,31 @@
         <v>उस पेज की उपशीर्षक पंक्ति</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Services Page Theme</v>
+      </c>
+      <c r="B18" t="str">
+        <v>civic</v>
+      </c>
+      <c r="C18" t="str">
+        <v>सार्वजनिक पेज का रंग-रूप: civic, slate या paper — सोसाइटी की थीम से अलग</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Services Page Sheets</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>कौन-कौन सी शीट सार्वजनिक पेज पर जाएँ (कॉमा से अलग)। खाली छोड़ें तो Services &amp; Help और _Town वाली शीट</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -408,6 +408,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -500,6 +508,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D17"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -749,6 +763,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -806,6 +829,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1026,6 +1054,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1088,6 +1123,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1168,7 +1209,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G40"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1241,148 +1291,148 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jangid</v>
+        <v>Vaibhav Pest Control</v>
       </c>
       <c r="B4" t="str">
-        <v>Carpenter</v>
+        <v>Pest Control</v>
       </c>
       <c r="C4" t="str">
-        <v>Repairs &amp; Maintenance</v>
+        <v>Building Services</v>
       </c>
       <c r="D4" t="str">
-        <v>₹150 / visit</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>On call</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>9922690290</v>
       </c>
       <c r="G4" t="str">
-        <v>Furniture repair and fittings</v>
+        <v>Quarterly society drive is free</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Otis Service</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>Lift Technician</v>
+        <v>Gardener</v>
       </c>
       <c r="C5" t="str">
         <v>Building Services</v>
       </c>
       <c r="D5" t="str">
-        <v>Society AMC</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>4-hour response</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>Report faults to the manager first</v>
+        <v>Balcony and terrace plants</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HiCare</v>
+        <v/>
       </c>
       <c r="B6" t="str">
-        <v>Pest Control</v>
+        <v>Gas Agency</v>
       </c>
       <c r="C6" t="str">
-        <v>Building Services</v>
+        <v>Utilities</v>
       </c>
       <c r="D6" t="str">
-        <v>₹1,200 / flat</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>By appointment</v>
+        <v/>
       </c>
       <c r="F6" t="str">
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>Quarterly society drive is free</v>
+        <v>Leak helpline 1800 22 9944</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Shanti Devi</v>
+        <v>Akka Maushi</v>
       </c>
       <c r="B7" t="str">
-        <v>Housekeeping</v>
+        <v>Maid</v>
       </c>
       <c r="C7" t="str">
-        <v>Building Services</v>
+        <v>Home Help</v>
       </c>
       <c r="D7" t="str">
-        <v>Society staff</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>6 AM – 2 PM</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>9922090766</v>
       </c>
       <c r="G7" t="str">
-        <v>Common areas and staircases</v>
+        <v>Sweeping, mopping, utensils</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Ganesh Pawar</v>
+        <v>Sunita Maushi</v>
       </c>
       <c r="B8" t="str">
-        <v>Gardener</v>
+        <v>Maid</v>
       </c>
       <c r="C8" t="str">
-        <v>Building Services</v>
+        <v>Home Help</v>
       </c>
       <c r="D8" t="str">
-        <v>₹80 / visit</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>Tue &amp; Sat mornings</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>7249544168</v>
       </c>
       <c r="G8" t="str">
-        <v>Balcony and terrace plants</v>
+        <v>Sweeping, mopping, utensils</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Jai Bhavani</v>
+        <v/>
       </c>
       <c r="B9" t="str">
-        <v>Water Tanker</v>
+        <v>Driver</v>
       </c>
       <c r="C9" t="str">
-        <v>Utilities</v>
+        <v>Home Help</v>
       </c>
       <c r="D9" t="str">
-        <v>₹900 / tanker</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>Same-day delivery</v>
+        <v/>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>10,000 litre tanker</v>
+        <v>Local trips, holds a valid licence</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>MSEDCL</v>
+        <v>aditya wireman</v>
       </c>
       <c r="B10" t="str">
-        <v>Electricity Board</v>
+        <v>Electrician</v>
       </c>
       <c r="C10" t="str">
         <v>Utilities</v>
@@ -1391,21 +1441,21 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>24x7 helpline</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>9325680187</v>
       </c>
       <c r="G10" t="str">
-        <v>Outages and meter faults</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mahanagar Gas</v>
+        <v>Awade mseb</v>
       </c>
       <c r="B11" t="str">
-        <v>Gas Agency</v>
+        <v>Electricity Board</v>
       </c>
       <c r="C11" t="str">
         <v>Utilities</v>
@@ -1414,202 +1464,685 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>24x7 for leaks</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>7875936797</v>
       </c>
       <c r="G11" t="str">
-        <v>Leak helpline 1800 22 9944</v>
+        <v>MSEB office awade</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>D. Kamble</v>
+        <v>Ramesh patil Boring</v>
       </c>
       <c r="B12" t="str">
-        <v>Society Manager</v>
+        <v/>
       </c>
       <c r="C12" t="str">
-        <v>Society Staff</v>
+        <v>Utilities</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Mon–Sat, 10 AM – 6 PM</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>9850929761</v>
       </c>
       <c r="G12" t="str">
-        <v>Maintenance bills, NOCs, complaints</v>
+        <v>Boring repair work</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>S. Rane</v>
+        <v>Ramesh patil Boring 1</v>
       </c>
       <c r="B13" t="str">
-        <v>Accountant</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>Society Staff</v>
+        <v/>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Tue &amp; Thu, 4 PM – 7 PM</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>9503814294</v>
       </c>
       <c r="G13" t="str">
-        <v>Dues, receipts, statements</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Sunita Bai</v>
+        <v>Vishal Boring Repare</v>
       </c>
       <c r="B14" t="str">
-        <v>Maid</v>
+        <v/>
       </c>
       <c r="C14" t="str">
-        <v>Home Help</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>₹50 / visit</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>7 AM – 11 AM</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>9028650650</v>
       </c>
       <c r="G14" t="str">
-        <v>Sweeping, mopping, utensils</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Lata Devi</v>
+        <v>Vinyak Boring Senser</v>
       </c>
       <c r="B15" t="str">
-        <v>Maid</v>
+        <v/>
       </c>
       <c r="C15" t="str">
-        <v>Home Help</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>₹60 / visit</v>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <v>6 AM – 10 AM</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>9168921005</v>
       </c>
       <c r="G15" t="str">
-        <v>Also irons clothes on request</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Kamla Bai</v>
+        <v>Ravi patil Boring Repare</v>
       </c>
       <c r="B16" t="str">
-        <v>Cook</v>
+        <v/>
       </c>
       <c r="C16" t="str">
-        <v>Home Help</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>₹2,500 / month</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>11 AM – 2 PM</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>8788731240</v>
       </c>
       <c r="G16" t="str">
-        <v>Vegetarian, two meals a day</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ganesh raju</v>
+        <v>Shrinivsh Boring</v>
       </c>
       <c r="B17" t="str">
-        <v>Car Cleaning</v>
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>Home Help</v>
+        <v/>
       </c>
       <c r="D17" t="str">
-        <v>₹500 / month</v>
+        <v/>
       </c>
       <c r="E17" t="str">
-        <v>6 AM – 9 AM</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>8855961649</v>
       </c>
       <c r="G17" t="str">
-        <v>Daily wash, interior weekly</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Deepak Sawant</v>
+        <v>Pravin Lavate IMC Clerk</v>
       </c>
       <c r="B18" t="str">
-        <v>Driver</v>
+        <v/>
       </c>
       <c r="C18" t="str">
-        <v>Home Help</v>
+        <v>Utilities</v>
       </c>
       <c r="D18" t="str">
-        <v>₹300 / trip</v>
+        <v/>
       </c>
       <c r="E18" t="str">
-        <v>By appointment</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>9922772149</v>
       </c>
       <c r="G18" t="str">
-        <v>Local trips, holds a valid licence</v>
+        <v>Property tax related officer</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Anita Kamble</v>
+        <v>Solanky Madam Sanitary Incepector IMC</v>
       </c>
       <c r="B19" t="str">
-        <v>Baby Sitter</v>
+        <v/>
       </c>
       <c r="C19" t="str">
-        <v>Home Help</v>
+        <v>Utilities</v>
       </c>
       <c r="D19" t="str">
-        <v>₹150 / hour</v>
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>Flexible</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>8329253329</v>
       </c>
       <c r="G19" t="str">
-        <v>Experienced with toddlers</v>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Ghanta Gadi Ankush Kurne</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>9146111279</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Garbage van</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Alliance Hospital Ich</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>Hospital</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>0230 2435001</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>mseb Wireman Rohit</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Electricity Board</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>9762315904</v>
+      </c>
+      <c r="G22" t="str">
+        <v>MSEB Wireman</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Ich S T Depot</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>0230 2432496</v>
+      </c>
+      <c r="G23" t="str">
+        <v xml:space="preserve">Bus depot </v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">Ich S T  Stand </v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>0230 2432202</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve">seva bharti Hospital </v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>Hospital</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>0230 2426171</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Ich S T Venktesh Parking Stand</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>8237744444</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Parking at bus stand</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>S T Ich</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>0230 2432202</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Aadhar Blood Bank Mete Saheb</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>8149370204</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Amrutmama Bhosale</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>Nagarsevak</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>9975067101</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Raju Pujari Balaji Bakery</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>Nagarsevak</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>9021543640</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Nagesh Patil Dada</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v>Nagarsevak</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>8888341342</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Nagesh Patil Dada</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>Nagarsevak</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>8888341342</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Santosh Shelke</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>Nagarsevak</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>9423040242</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>LV Gate Watchman Uttam</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>Society Staff</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>9595405090</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>LV Gate Watchman Umesh Patil</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>Society Staff</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>9970327078</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>LV Watchman Lokere</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>Society Staff</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>9075242921</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>L V Lift Shravani Costmer Care</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>Society Staff</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>7744888217</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>LV Lift Vijay Parker</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>Society Staff</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>8087508217</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>LV Lift Pradeep</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v>Society Staff</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>9082264006</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Police Crane Vishal</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>8421410046</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G40"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1617,6 +2150,27 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S21"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" customWidth="1"/>
+    <col min="19" max="19" width="17.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2867,6 +3421,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2912,6 +3473,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3001,6 +3572,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/data.xlsx
+++ b/data.xlsx
@@ -2149,7 +2149,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S28"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -3411,9 +3411,422 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Radheshyam Narayanlal Loya</v>
+      </c>
+      <c r="B22" t="str">
+        <v>B</v>
+      </c>
+      <c r="C22" t="str">
+        <v>B-5</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>9422414549</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>O+</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>prasad kulkarni</v>
+      </c>
+      <c r="B23" t="str">
+        <v>D</v>
+      </c>
+      <c r="C23" t="str">
+        <v>D10</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>8483098383</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>B +ve</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Gourav Pujari</v>
+      </c>
+      <c r="B24" t="str">
+        <v>D</v>
+      </c>
+      <c r="C24" t="str">
+        <v>D-18</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>7276440440</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Nilesh Suresh Koshti</v>
+      </c>
+      <c r="B25" t="str">
+        <v>D</v>
+      </c>
+      <c r="C25" t="str">
+        <v>D6</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>8600204473</v>
+      </c>
+      <c r="F25" t="str">
+        <v>nilesh2348@gmail.com</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>4</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Adv. Omkar Smita Mahaveer Kurade</v>
+      </c>
+      <c r="B26" t="str">
+        <v>A</v>
+      </c>
+      <c r="C26" t="str">
+        <v>A-8</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>9762226311</v>
+      </c>
+      <c r="F26" t="str">
+        <v>advomkarkurade@gmail.com</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>Advocate</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>4</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Shashikant Joshi</v>
+      </c>
+      <c r="B27" t="str">
+        <v>C</v>
+      </c>
+      <c r="C27" t="str">
+        <v>B-12</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>9011074074</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>4</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Vishal Suresh kolekar</v>
+      </c>
+      <c r="B28" t="str">
+        <v>D</v>
+      </c>
+      <c r="C28" t="str">
+        <v>D 7</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>9623880919</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>AB+</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>3</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S28"/>
   </ignoredErrors>
 </worksheet>
 </file>
